--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260910.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260910.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.99%</t>
+          <t>11.02%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.44%</t>
+          <t>10.32%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.09%</t>
+          <t>7.77%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.57%</t>
+          <t>7.61%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.49%</t>
+          <t>5.58%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.49%</t>
+          <t>4.39%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.26%</t>
+          <t>4.29%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.38%</t>
+          <t>3.42%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.18%</t>
+          <t>3.17%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>3.03%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.59%</t>
+          <t>2.64%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>2.32%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>2.23%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>2.05%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.74%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.63%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.36%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.25%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.23%</t>
         </is>
       </c>
     </row>
@@ -1041,44 +1041,44 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>TTEK UW</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>德照科技公司</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>32,510</t>
+          <t>95,263</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.18%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TTEK UW</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>德照科技公司</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>95,263</t>
+          <t>32,510</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.18%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.13%</t>
         </is>
       </c>
     </row>
@@ -1151,39 +1151,39 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>EIX US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>愛迪生國際</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>27,569</t>
+          <t>51,310</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>EIX US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>愛迪生國際</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>51,310</t>
+          <t>27,569</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
@@ -1254,51 +1254,51 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>EVRG US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>Evergy公司</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>9,004</t>
+          <t>30,314</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>EVRG US</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Evergy公司</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>30,314</t>
+          <t>9,004</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.72%</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.60%</t>
         </is>
       </c>
     </row>
@@ -1481,44 +1481,44 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>PNW US</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>皮那可資本公司</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>13,424</t>
+          <t>16,127</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.54%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>PNW US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>皮那可資本公司</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>16,127</t>
+          <t>13,424</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.52%</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.36%</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.30%</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       <c r="B72" s="3" t="inlineStr"/>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>120,933,430</t>
+          <t>120,860,143</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
